--- a/docs/舰装-舰装核心.xlsx
+++ b/docs/舰装-舰装核心.xlsx
@@ -1919,8 +1919,10 @@
       <x:c r="B32" s="4" t="str">
         <x:v>Shift 详情</x:v>
       </x:c>
-      <x:c r="C32" s="4" t="str">
-        <x:v>隐去灰色通称，显示真实舰名、船型、舰种、熟练度、最终耐久/装甲/航速、燃油量、四区占用格数。</x:v>
+      <x:c r="C32" s="4" t="inlineStr">
+        <x:is>
+          <x:t>首行按舰名ID读取独立舰级说明，中文逐字沿用舰R百科；其后显示分类、熟练度、最终属性、燃油及四区占用。标题仍为舰名，物品不增加字段。</x:t>
+        </x:is>
       </x:c>
       <x:c r="D32" s="4" t="str">
         <x:v>已实现</x:v>
